--- a/budget/walch.xlsx
+++ b/budget/walch.xlsx
@@ -20,11 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">PhD 12 Monate</t>
   </si>
   <si>
+    <t xml:space="preserve"> (valorisiert)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restmittel</t>
   </si>
   <si>
@@ -34,7 +37,7 @@
     <t xml:space="preserve">Anstellung bis 31.3. 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">Armin 10 Monate</t>
+    <t xml:space="preserve">Armin 9 Monate</t>
   </si>
   <si>
     <t xml:space="preserve">Anstellung bis 31.1. 2027</t>
@@ -47,14 +50,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -114,8 +119,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -245,56 +262,60 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="n">
-        <v>50220</v>
+      <c r="B1" s="1" t="n">
+        <f aca="false">50220*1.0425</f>
+        <v>52354.35</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>74373</v>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>76669.23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <f aca="false">B1/2</f>
-        <v>25110</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="3" t="n">
+        <f aca="false">B1</f>
+        <v>52354.35</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <f aca="false">(B1/12)*10</f>
-        <v>41850</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5" s="3" t="n">
+        <f aca="false">(B1/12)*9</f>
+        <v>39265.7625</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="n">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <f aca="false">B2-B4-B5</f>
-        <v>7413</v>
+        <v>-14950.8825</v>
       </c>
     </row>
   </sheetData>

--- a/budget/walch.xlsx
+++ b/budget/walch.xlsx
@@ -31,16 +31,16 @@
     <t xml:space="preserve">Restmittel</t>
   </si>
   <si>
-    <t xml:space="preserve">Matthias 6 Monate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anstellung bis 31.3. 2027</t>
+    <t xml:space="preserve">Matthias 9 Monate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anstellung bis 30. 6. 2027</t>
   </si>
   <si>
     <t xml:space="preserve">Armin 9 Monate</t>
   </si>
   <si>
-    <t xml:space="preserve">Anstellung bis 31.1. 2027</t>
+    <t xml:space="preserve">Anstellung bis 31.12. 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Verfügbar</t>
@@ -290,8 +290,8 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="n">
-        <f aca="false">B1</f>
-        <v>52354.35</v>
+        <f aca="false">B1/12*9</f>
+        <v>39265.7625</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
@@ -315,7 +315,7 @@
       </c>
       <c r="B7" s="3" t="n">
         <f aca="false">B2-B4-B5</f>
-        <v>-14950.8825</v>
+        <v>-1862.29500000001</v>
       </c>
     </row>
   </sheetData>

--- a/budget/walch.xlsx
+++ b/budget/walch.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t xml:space="preserve">PhD 12 Monate</t>
   </si>
@@ -128,7 +128,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -259,10 +259,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -270,52 +270,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="n">
-        <f aca="false">50220*1.0425</f>
-        <v>52354.35</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
+        <v>50220</v>
+      </c>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <f aca="false">B1*1.0425</f>
+        <v>52354.35</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B3" s="1" t="n">
         <v>76669.23</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <f aca="false">B1/12*9</f>
-        <v>39265.7625</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <f aca="false">B1/12*3+B2/12*6</f>
+        <v>38732.175</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <f aca="false">(B1/12)*9</f>
-        <v>39265.7625</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B6" s="3" t="n">
+        <v>38963.16</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="n">
-        <f aca="false">B2-B4-B5</f>
-        <v>-1862.29500000001</v>
+      <c r="B8" s="3" t="n">
+        <f aca="false">B3-B5-B6</f>
+        <v>-1026.10500000001</v>
       </c>
     </row>
   </sheetData>

--- a/budget/walch.xlsx
+++ b/budget/walch.xlsx
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+  <si>
+    <t xml:space="preserve">Stand: 4.5.2026</t>
+  </si>
   <si>
     <t xml:space="preserve">PhD 12 Monate</t>
   </si>
@@ -259,7 +262,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.34"/>
@@ -269,61 +272,72 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="n">
-        <v>50220</v>
-      </c>
+      <c r="B1" s="1"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">B1*1.0425</f>
-        <v>52354.35</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>50220</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <f aca="false">B3*1.0425</f>
+        <v>52354.35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>76669.23</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <f aca="false">B1/12*3+B2/12*6</f>
+      <c r="B5" s="1" t="n">
+        <v>37701.79</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <f aca="false">B3/12*3+B4/12*6</f>
         <v>38732.175</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>38963.16</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="n">
-        <f aca="false">B3-B5-B6</f>
-        <v>-1026.10500000001</v>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <f aca="false">B5-B7-B8</f>
+        <v>-1030.385</v>
       </c>
     </row>
   </sheetData>
